--- a/resultados/anahy/inventario_links.xlsx
+++ b/resultados/anahy/inventario_links.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:01:27</t>
+          <t>2026-08-03 01:17:03</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://anahy.atende.net/cidadao/acesso-informacao/perguntas-frequentes?rot=1&amp;aca=119&amp;ajax=t&amp;processo=viewFile&amp;file=601EC2BDD464453E0595AEA7010231FFDE804819&amp;sistema=WPO&amp;classe=UploadMidia</t>
+          <t>https://anahy.atende.net/cidadao/noticia/atende.php?rot=1&amp;aca=119&amp;ajax=t&amp;processo=viewFile&amp;file=371191543602A124ACA70346A17C4608338B21BA&amp;sistema=WPO&amp;classe=UploadMidia</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -522,14 +522,14 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
         <v>200</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-07-30 11:01:34</t>
+          <t>2026-08-03 01:18:41</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://anahy.atende.net/cidadao/acesso-informacao/obras-acoes?rot=1&amp;aca=119&amp;ajax=t&amp;processo=viewFile&amp;file=601EC2BDD464453E0595AEA7010231FFDE804819&amp;sistema=WPO&amp;classe=UploadMidia</t>
+          <t>https://anahy.atende.net/cidadao/acesso-informacao/conheca-a-lei?rot=1&amp;aca=119&amp;ajax=t&amp;processo=viewFile&amp;file=601EC2BDD464453E0595AEA7010231FFDE804819&amp;sistema=WPO&amp;classe=UploadMidia</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -557,224 +557,14 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>200</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-07-30 11:01:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://anahy.atende.net/cidadao/noticia/atende.php?rot=1&amp;aca=119&amp;ajax=t&amp;processo=viewFile&amp;file=371191543602A124ACA70346A17C4608338B21BA&amp;sistema=WPO&amp;classe=UploadMidia</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>anahy.atende.net</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>.pdf</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>200</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-07-30 11:02:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://anahy.atende.net/cidadao/acesso-informacao/conheca-a-lei?rot=1&amp;aca=119&amp;ajax=t&amp;processo=viewFile&amp;file=601EC2BDD464453E0595AEA7010231FFDE804819&amp;sistema=WPO&amp;classe=UploadMidia</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>anahy.atende.net</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>.pdf</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>200</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-07-30 11:10:57</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/acesso-informacao/perguntas-frequentes?rot=1&amp;aca=119&amp;ajax=t&amp;processo=viewFile&amp;file=601EC2BDD464453E0595AEA7010231FFDE804819&amp;sistema=WPO&amp;classe=UploadMidia</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>nfse-anahy.atende.net</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>.pdf</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" t="n">
-        <v>200</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:23:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/acesso-informacao?rot=1&amp;aca=119&amp;ajax=t&amp;processo=viewFile&amp;file=601EC2BDD464453E0595AEA7010231FFDE804819&amp;sistema=WPO&amp;classe=UploadMidia</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>nfse-anahy.atende.net</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>.pdf</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>7</v>
-      </c>
-      <c r="H8" t="n">
-        <v>200</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:32:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/acesso-informacao/conheca-a-lei?rot=1&amp;aca=119&amp;ajax=t&amp;processo=viewFile&amp;file=601EC2BDD464453E0595AEA7010231FFDE804819&amp;sistema=WPO&amp;classe=UploadMidia</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>nfse-anahy.atende.net</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>.pdf</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" t="n">
-        <v>200</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:33:06</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>anahy</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://nfse-anahy.atende.net/cidadao/noticia/atende.php?rot=1&amp;aca=119&amp;ajax=t&amp;processo=viewFile&amp;file=371191543602A124ACA70346A17C4608338B21BA&amp;sistema=WPO&amp;classe=UploadMidia</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>nfse-anahy.atende.net</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>.pdf</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>8</v>
-      </c>
-      <c r="H10" t="n">
-        <v>200</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:33:52</t>
+          <t>2026-08-03 01:26:54</t>
         </is>
       </c>
     </row>
